--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/panel_11/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Front_Summary.xlsx
@@ -413,690 +413,736 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="C1" t="inlineStr">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Measured by operator 7 on tool HRM-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Max Stepheight</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Min Stepheight</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Mean Stepheight</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Radius</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Dimple</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Pad 1</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>16.99598</v>
-      </c>
-      <c r="D2" t="n">
-        <v>16.4434</v>
-      </c>
-      <c r="E2" t="n">
-        <v>16.38873</v>
-      </c>
-      <c r="F2" t="n">
-        <v>42.0515</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.05065</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.82018</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pad 1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.88575</v>
+        <v>16.95525</v>
       </c>
       <c r="D3" t="n">
-        <v>16.73692</v>
+        <v>16.68681</v>
       </c>
       <c r="E3" t="n">
-        <v>16.65372</v>
+        <v>16.78909</v>
       </c>
       <c r="F3" t="n">
-        <v>43.59333</v>
+        <v>41.98369</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05061</v>
+        <v>0.05119</v>
       </c>
       <c r="H3" t="n">
-        <v>1.79723</v>
+        <v>1.84242</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.67818</v>
+        <v>16.89198</v>
       </c>
       <c r="D4" t="n">
-        <v>16.6859</v>
+        <v>16.52004</v>
       </c>
       <c r="E4" t="n">
-        <v>16.75041</v>
+        <v>16.70947</v>
       </c>
       <c r="F4" t="n">
-        <v>42.8697</v>
+        <v>43.24051</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05104</v>
+        <v>0.05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.82706</v>
+        <v>1.82151</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.51085</v>
+        <v>17.18233</v>
       </c>
       <c r="D5" t="n">
-        <v>16.54447</v>
+        <v>16.10943</v>
       </c>
       <c r="E5" t="n">
-        <v>16.58106</v>
+        <v>16.72213</v>
       </c>
       <c r="F5" t="n">
-        <v>42.76001</v>
+        <v>42.72743</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05105</v>
+        <v>0.05197</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81729</v>
+        <v>1.84762</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.73412</v>
+        <v>17.02441</v>
       </c>
       <c r="D6" t="n">
-        <v>16.24694</v>
+        <v>16.62737</v>
       </c>
       <c r="E6" t="n">
-        <v>17.02602</v>
+        <v>16.69626</v>
       </c>
       <c r="F6" t="n">
-        <v>42.63113</v>
+        <v>42.04861</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05023</v>
+        <v>0.05059</v>
       </c>
       <c r="H6" t="n">
-        <v>1.84747</v>
+        <v>1.77607</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.58614</v>
+        <v>16.83083</v>
       </c>
       <c r="D7" t="n">
-        <v>16.48066</v>
+        <v>16.60372</v>
       </c>
       <c r="E7" t="n">
-        <v>16.66358</v>
+        <v>16.79287</v>
       </c>
       <c r="F7" t="n">
-        <v>42.50109</v>
+        <v>42.64002</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04935</v>
+        <v>0.05051</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83348</v>
+        <v>1.83555</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.90178</v>
+        <v>16.57707</v>
       </c>
       <c r="D8" t="n">
-        <v>16.69214</v>
+        <v>16.40452</v>
       </c>
       <c r="E8" t="n">
-        <v>17.12478</v>
+        <v>16.54202</v>
       </c>
       <c r="F8" t="n">
-        <v>41.92366</v>
+        <v>42.41163</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05087</v>
+        <v>0.04929</v>
       </c>
       <c r="H8" t="n">
-        <v>1.80914</v>
+        <v>1.80203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.10617</v>
+        <v>17.06374</v>
       </c>
       <c r="D9" t="n">
-        <v>16.59573</v>
+        <v>16.49361</v>
       </c>
       <c r="E9" t="n">
-        <v>16.80438</v>
+        <v>16.68389</v>
       </c>
       <c r="F9" t="n">
-        <v>42.50872</v>
+        <v>43.64833</v>
       </c>
       <c r="G9" t="n">
-        <v>0.04995</v>
+        <v>0.0507</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79493</v>
+        <v>1.77706</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>16.96972</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16.30056</v>
+      </c>
+      <c r="E10" t="n">
+        <v>16.7993</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42.33821</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.05065</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.82159</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C10" t="n">
-        <v>17.06897</v>
-      </c>
-      <c r="D10" t="n">
-        <v>16.55235</v>
-      </c>
-      <c r="E10" t="n">
-        <v>16.82699</v>
-      </c>
-      <c r="F10" t="n">
-        <v>42.86701</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.05006</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.83296</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Max Stepheight</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Space</t>
-        </is>
+      <c r="C11" t="n">
+        <v>16.76036</v>
+      </c>
+      <c r="D11" t="n">
+        <v>16.5767</v>
+      </c>
+      <c r="E11" t="n">
+        <v>16.75772</v>
+      </c>
+      <c r="F11" t="n">
+        <v>43.2291</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.05001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.83717</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Trace 1</t>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bump</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Unit 8</t>
-        </is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>0.59977</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.12908</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Unit 9</t>
-        </is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>0.60987</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.13913</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Unit 4</t>
-        </is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>0.61163</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.08988</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Unit 5</t>
-        </is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>0.60831</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.10261</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Unit 6</t>
-        </is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.59411</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.10395</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Unit 1</t>
-        </is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.60738</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.11769</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Unit 2</t>
-        </is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>0.60864</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.10419</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.60416</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.12427</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="C21" t="inlineStr">
+      <c r="C21" t="n">
+        <v>0.60585</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.1178</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Rz max</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Rz mean</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Rz min</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>Rz max</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Ra mean</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Ra Std dev</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Ra min</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Ra max</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Unit 7</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>roughness</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.75518</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.08227</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.60202</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.96826</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.10825</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.00763</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.09315</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0.12477</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Unit 8</t>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>roughness</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.76593</v>
+        <v>0.75604</v>
       </c>
       <c r="D23" t="n">
-        <v>0.07986</v>
+        <v>0.08222</v>
       </c>
       <c r="E23" t="n">
-        <v>0.60616</v>
+        <v>0.62865</v>
       </c>
       <c r="F23" t="n">
-        <v>0.97886</v>
+        <v>0.95445</v>
       </c>
       <c r="G23" t="n">
-        <v>0.11154</v>
+        <v>0.10691</v>
       </c>
       <c r="H23" t="n">
-        <v>0.00743</v>
+        <v>0.00746</v>
       </c>
       <c r="I23" t="n">
-        <v>0.09182999999999999</v>
+        <v>0.09359000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0.12472</v>
+        <v>0.12408</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Unit 9</t>
+          <t>Unit 8</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.75431</v>
+        <v>0.74354</v>
       </c>
       <c r="D24" t="n">
-        <v>0.08074000000000001</v>
+        <v>0.08184</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6138</v>
+        <v>0.60867</v>
       </c>
       <c r="F24" t="n">
-        <v>0.95263</v>
+        <v>0.96834</v>
       </c>
       <c r="G24" t="n">
-        <v>0.10934</v>
+        <v>0.1081</v>
       </c>
       <c r="H24" t="n">
-        <v>0.00756</v>
+        <v>0.00738</v>
       </c>
       <c r="I24" t="n">
-        <v>0.09288</v>
+        <v>0.09370000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.12518</v>
+        <v>0.1293</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Unit 4</t>
+          <t>Unit 9</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.75478</v>
+        <v>0.75576</v>
       </c>
       <c r="D25" t="n">
-        <v>0.08003</v>
+        <v>0.08054</v>
       </c>
       <c r="E25" t="n">
-        <v>0.60265</v>
+        <v>0.61516</v>
       </c>
       <c r="F25" t="n">
-        <v>0.96899</v>
+        <v>0.95749</v>
       </c>
       <c r="G25" t="n">
-        <v>0.10892</v>
+        <v>0.11145</v>
       </c>
       <c r="H25" t="n">
-        <v>0.00763</v>
+        <v>0.00753</v>
       </c>
       <c r="I25" t="n">
-        <v>0.09258</v>
+        <v>0.09134</v>
       </c>
       <c r="J25" t="n">
-        <v>0.12538</v>
+        <v>0.12382</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Unit 5</t>
+          <t>Unit 4</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.72305</v>
+        <v>0.73982</v>
       </c>
       <c r="D26" t="n">
-        <v>0.08115</v>
+        <v>0.08137999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>0.60505</v>
+        <v>0.59437</v>
       </c>
       <c r="F26" t="n">
-        <v>0.95365</v>
+        <v>0.95581</v>
       </c>
       <c r="G26" t="n">
-        <v>0.10903</v>
+        <v>0.10788</v>
       </c>
       <c r="H26" t="n">
-        <v>0.00772</v>
+        <v>0.00768</v>
       </c>
       <c r="I26" t="n">
-        <v>0.09118</v>
+        <v>0.09455</v>
       </c>
       <c r="J26" t="n">
-        <v>0.12727</v>
+        <v>0.12489</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Unit 6</t>
+          <t>Unit 5</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.75117</v>
+        <v>0.76656</v>
       </c>
       <c r="D27" t="n">
-        <v>0.08237</v>
+        <v>0.08087999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>0.61181</v>
+        <v>0.6138400000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9731</v>
+        <v>0.9662500000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>0.10957</v>
+        <v>0.10966</v>
       </c>
       <c r="H27" t="n">
-        <v>0.00754</v>
+        <v>0.00744</v>
       </c>
       <c r="I27" t="n">
-        <v>0.09239</v>
+        <v>0.09021999999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>0.12778</v>
+        <v>0.12734</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Unit 1</t>
+          <t>Unit 6</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.7561600000000001</v>
+        <v>0.7491</v>
       </c>
       <c r="D28" t="n">
-        <v>0.08021</v>
+        <v>0.08023</v>
       </c>
       <c r="E28" t="n">
-        <v>0.61014</v>
+        <v>0.60815</v>
       </c>
       <c r="F28" t="n">
-        <v>0.96099</v>
+        <v>0.96724</v>
       </c>
       <c r="G28" t="n">
-        <v>0.11126</v>
+        <v>0.11026</v>
       </c>
       <c r="H28" t="n">
-        <v>0.00766</v>
+        <v>0.00765</v>
       </c>
       <c r="I28" t="n">
-        <v>0.09204</v>
+        <v>0.09156</v>
       </c>
       <c r="J28" t="n">
-        <v>0.12419</v>
+        <v>0.12362</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Unit 2</t>
+          <t>Unit 1</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.75142</v>
+        <v>0.75902</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0799</v>
+        <v>0.08015</v>
       </c>
       <c r="E29" t="n">
-        <v>0.60907</v>
+        <v>0.60829</v>
       </c>
       <c r="F29" t="n">
-        <v>0.96783</v>
+        <v>0.94646</v>
       </c>
       <c r="G29" t="n">
-        <v>0.10986</v>
+        <v>0.1093</v>
       </c>
       <c r="H29" t="n">
-        <v>0.00764</v>
+        <v>0.00736</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09304</v>
+        <v>0.093</v>
       </c>
       <c r="J29" t="n">
-        <v>0.12661</v>
+        <v>0.12526</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>0.75697</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.08119</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.60449</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.94486</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.10818</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.00764</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.12649</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>Unit 3</t>
         </is>
       </c>
-      <c r="C30" t="n">
-        <v>0.7563299999999999</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.08008999999999999</v>
-      </c>
-      <c r="E30" t="n">
-        <v>0.60325</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.95707</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0.10885</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.00772</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.0931</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0.12691</v>
+      <c r="C31" t="n">
+        <v>0.7451</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.08084</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.61385</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.97628</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.10857</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.00766</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09184</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.12634</v>
       </c>
     </row>
   </sheetData>
